--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8571,0.0819,0.0514,0.0041</t>
-  </si>
-  <si>
-    <t>0.7797,0.0881,0.0262,0.0145</t>
-  </si>
-  <si>
-    <t>0.8954,0.0237,0.0704,0.0010</t>
-  </si>
-  <si>
-    <t>0.9168,0.0348,0.0268,0.0009</t>
-  </si>
-  <si>
-    <t>0.8427,0.1021,0.0465,0.0058</t>
-  </si>
-  <si>
-    <t>0.8302,0.0840,0.0398,0.0047</t>
-  </si>
-  <si>
-    <t>0.7420,0.1079,0.0623,0.0134</t>
-  </si>
-  <si>
-    <t>0.8253,0.0906,0.0436,0.0051</t>
-  </si>
-  <si>
-    <t>0.7557,0.1272,0.0557,0.0108</t>
-  </si>
-  <si>
-    <t>0.5162,0.4183,0.0748,0.0151</t>
-  </si>
-  <si>
-    <t>0.6704,0.1667,0.0604,0.0241</t>
-  </si>
-  <si>
-    <t>0.7990,0.0714,0.0379,0.0132</t>
-  </si>
-  <si>
-    <t>0.9438,0.0199,0.0342,0.0003</t>
-  </si>
-  <si>
-    <t>0.7913,0.1150,0.0935,0.0022</t>
-  </si>
-  <si>
-    <t>0.7804,0.0399,0.1917,0.0004</t>
-  </si>
-  <si>
-    <t>0.6795,0.0355,0.4212,0.0004</t>
-  </si>
-  <si>
-    <t>0.8797,0.0498,0.0657,0.0003</t>
-  </si>
-  <si>
-    <t>0.1627,0.9038,0.0545,0.0007</t>
-  </si>
-  <si>
-    <t>0.6282,0.4945,0.0369,0.0004</t>
-  </si>
-  <si>
-    <t>0.6501,0.3106,0.0791,0.0070</t>
-  </si>
-  <si>
-    <t>0.1708,0.8594,0.1433,0.0029</t>
-  </si>
-  <si>
-    <t>0.3048,0.7678,0.1377,0.0013</t>
-  </si>
-  <si>
-    <t>0.9519,0.0160,0.0241,0.0001</t>
-  </si>
-  <si>
-    <t>0.9767,0.0072,0.0111,0.0001</t>
-  </si>
-  <si>
-    <t>0.9465,0.0124,0.0392,0.0003</t>
-  </si>
-  <si>
-    <t>0.8795,0.0376,0.0664,0.0002</t>
-  </si>
-  <si>
-    <t>0.9333,0.0111,0.0573,0.0001</t>
-  </si>
-  <si>
-    <t>0.8701,0.0109,0.1465,0.0009</t>
-  </si>
-  <si>
-    <t>0.8521,0.0038,0.2273,0.0003</t>
-  </si>
-  <si>
-    <t>0.8036,0.1708,0.0484,0.0019</t>
-  </si>
-  <si>
-    <t>0.9134,0.0734,0.0233,0.0005</t>
-  </si>
-  <si>
-    <t>0.2612,0.5225,0.5620,0.0207</t>
-  </si>
-  <si>
-    <t>0.5288,0.5383,0.0810,0.0008</t>
-  </si>
-  <si>
-    <t>0.9438,0.0269,0.0099,0.0017</t>
-  </si>
-  <si>
-    <t>0.6778,0.1648,0.2718,0.0068</t>
-  </si>
-  <si>
-    <t>0.7299,0.2396,0.0585,0.0050</t>
-  </si>
-  <si>
-    <t>0.8376,0.1602,0.0189,0.0007</t>
-  </si>
-  <si>
-    <t>0.8539,0.1925,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.9740,0.0009,0.0233,0.0001</t>
-  </si>
-  <si>
-    <t>0.9531,0.0068,0.0347,0.0001</t>
-  </si>
-  <si>
-    <t>0.9895,0.0009,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.9005,0.0253,0.0844,0.0001</t>
-  </si>
-  <si>
-    <t>0.5131,0.4548,0.0590,0.0009</t>
-  </si>
-  <si>
-    <t>0.9558,0.0021,0.0731,0.0001</t>
-  </si>
-  <si>
-    <t>0.9375,0.0291,0.0253,0.0006</t>
-  </si>
-  <si>
-    <t>0.8817,0.1578,0.0138,0.0002</t>
-  </si>
-  <si>
-    <t>0.1792,0.9033,0.0607,0.0008</t>
-  </si>
-  <si>
-    <t>0.7223,0.4022,0.0266,0.0002</t>
-  </si>
-  <si>
-    <t>0.7711,0.0399,0.1264,0.0003</t>
-  </si>
-  <si>
-    <t>0.9333,0.0109,0.0504,0.0001</t>
-  </si>
-  <si>
-    <t>0.9362,0.0050,0.0548,0.0003</t>
-  </si>
-  <si>
-    <t>0.8230,0.0123,0.2180,0.0001</t>
-  </si>
-  <si>
-    <t>0.5673,0.0386,0.4898,0.0006</t>
-  </si>
-  <si>
-    <t>0.8840,0.0076,0.1412,0.0003</t>
-  </si>
-  <si>
-    <t>0.7157,0.2358,0.0603,0.0048</t>
-  </si>
-  <si>
-    <t>0.6815,0.2265,0.0953,0.0045</t>
-  </si>
-  <si>
-    <t>0.6764,0.1590,0.0878,0.0127</t>
-  </si>
-  <si>
-    <t>0.3933,0.3783,0.4134,0.0041</t>
-  </si>
-  <si>
-    <t>0.6529,0.2627,0.0514,0.0090</t>
-  </si>
-  <si>
-    <t>0.8326,0.1152,0.0391,0.0032</t>
-  </si>
-  <si>
-    <t>0.7362,0.1132,0.1095,0.0101</t>
-  </si>
-  <si>
-    <t>0.0835,0.4394,0.7568,0.0001</t>
-  </si>
-  <si>
-    <t>0.3666,0.0478,0.6974,0.0002</t>
-  </si>
-  <si>
-    <t>0.7680,0.0596,0.1715,0.0047</t>
-  </si>
-  <si>
-    <t>0.3006,0.2851,0.4294,0.0004</t>
-  </si>
-  <si>
-    <t>0.7298,0.0116,0.3493,0.0003</t>
-  </si>
-  <si>
-    <t>0.8902,0.0924,0.0347,0.0003</t>
-  </si>
-  <si>
-    <t>0.0082,0.9904,0.0209,0.0004</t>
-  </si>
-  <si>
-    <t>0.9538,0.0194,0.0116,0.0010</t>
-  </si>
-  <si>
-    <t>0.7666,0.1709,0.0863,0.0021</t>
-  </si>
-  <si>
-    <t>0.3918,0.1627,0.6135,0.0029</t>
-  </si>
-  <si>
-    <t>0.1384,0.7509,0.2734,0.0005</t>
-  </si>
-  <si>
-    <t>0.7787,0.0716,0.0939,0.0002</t>
-  </si>
-  <si>
-    <t>0.2572,0.7481,0.0419,0.0001</t>
-  </si>
-  <si>
-    <t>0.9036,0.0307,0.0422,0.0002</t>
-  </si>
-  <si>
-    <t>0.9456,0.0100,0.0293,0.0007</t>
-  </si>
-  <si>
-    <t>0.9495,0.0123,0.0136,0.0020</t>
-  </si>
-  <si>
-    <t>0.9617,0.0215,0.0094,0.0007</t>
-  </si>
-  <si>
-    <t>0.9402,0.0250,0.0121,0.0025</t>
-  </si>
-  <si>
-    <t>0.8629,0.0629,0.0395,0.0056</t>
-  </si>
-  <si>
-    <t>0.9512,0.0281,0.0085,0.0010</t>
-  </si>
-  <si>
-    <t>0.7520,0.0889,0.1115,0.0002</t>
-  </si>
-  <si>
-    <t>0.8938,0.0067,0.1286,0.0001</t>
-  </si>
-  <si>
-    <t>0.7271,0.0216,0.3550,0.0002</t>
-  </si>
-  <si>
-    <t>0.7816,0.0129,0.2848,0.0002</t>
-  </si>
-  <si>
-    <t>0.3696,0.5053,0.0819,0.0002</t>
-  </si>
-  <si>
-    <t>0.7524,0.1377,0.0750,0.0002</t>
-  </si>
-  <si>
-    <t>0.8724,0.0712,0.0162,0.0046</t>
-  </si>
-  <si>
-    <t>0.6965,0.2207,0.1034,0.0052</t>
-  </si>
-  <si>
-    <t>0.6239,0.2752,0.0617,0.0083</t>
-  </si>
-  <si>
-    <t>0.6404,0.1397,0.0529,0.0249</t>
-  </si>
-  <si>
-    <t>0.7187,0.1434,0.0775,0.0165</t>
-  </si>
-  <si>
-    <t>0.5479,0.1459,0.0610,0.0570</t>
-  </si>
-  <si>
-    <t>0.7588,0.0911,0.0535,0.0176</t>
-  </si>
-  <si>
-    <t>0.7077,0.1334,0.0524,0.0172</t>
-  </si>
-  <si>
-    <t>0.5426,0.4420,0.0766,0.0071</t>
-  </si>
-  <si>
-    <t>0.9070,0.0268,0.0248,0.0047</t>
-  </si>
-  <si>
-    <t>0.8208,0.0343,0.0246,0.0165</t>
-  </si>
-  <si>
-    <t>0.8431,0.0515,0.0264,0.0125</t>
-  </si>
-  <si>
-    <t>0.7953,0.1308,0.0514,0.0045</t>
-  </si>
-  <si>
-    <t>0.7308,0.0968,0.0543,0.0301</t>
-  </si>
-  <si>
-    <t>0.7131,0.1102,0.0445,0.0188</t>
-  </si>
-  <si>
-    <t>0.8076,0.1053,0.0407,0.0093</t>
-  </si>
-  <si>
-    <t>0.1041,0.1463,0.8847,0.0078</t>
-  </si>
-  <si>
-    <t>0.7920,0.0300,0.2208,0.0014</t>
-  </si>
-  <si>
-    <t>0.9829,0.0036,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9707,0.0035,0.0196,0.0001</t>
-  </si>
-  <si>
-    <t>0.6061,0.4820,0.0460,0.0013</t>
-  </si>
-  <si>
-    <t>0.3233,0.7173,0.1244,0.0043</t>
-  </si>
-  <si>
-    <t>0.7545,0.2410,0.0546,0.0020</t>
-  </si>
-  <si>
-    <t>0.3272,0.7425,0.1205,0.0023</t>
-  </si>
-  <si>
-    <t>0.1911,0.8262,0.1043,0.0039</t>
-  </si>
-  <si>
-    <t>0.0932,0.9329,0.0474,0.0010</t>
-  </si>
-  <si>
-    <t>0.6436,0.3227,0.1094,0.0019</t>
-  </si>
-  <si>
-    <t>0.8929,0.0673,0.0424,0.0007</t>
-  </si>
-  <si>
-    <t>0.8584,0.0671,0.0818,0.0009</t>
-  </si>
-  <si>
-    <t>0.8768,0.1117,0.0364,0.0005</t>
-  </si>
-  <si>
-    <t>0.9467,0.0231,0.0280,0.0002</t>
-  </si>
-  <si>
-    <t>0.9169,0.0373,0.0267,0.0014</t>
-  </si>
-  <si>
-    <t>0.4692,0.6781,0.0527,0.0004</t>
-  </si>
-  <si>
-    <t>0.4225,0.6480,0.0944,0.0011</t>
-  </si>
-  <si>
-    <t>0.8388,0.1695,0.0431,0.0010</t>
-  </si>
-  <si>
-    <t>0.1855,0.3841,0.7676,0.0025</t>
-  </si>
-  <si>
-    <t>0.8731,0.0975,0.0272,0.0013</t>
-  </si>
-  <si>
-    <t>0.7827,0.1890,0.0655,0.0034</t>
-  </si>
-  <si>
-    <t>0.6984,0.2852,0.0872,0.0025</t>
-  </si>
-  <si>
-    <t>0.9248,0.0504,0.0124,0.0019</t>
-  </si>
-  <si>
-    <t>0.8646,0.0281,0.0257,0.0122</t>
-  </si>
-  <si>
-    <t>0.7674,0.1636,0.0532,0.0046</t>
-  </si>
-  <si>
-    <t>0.8334,0.0917,0.0326,0.0047</t>
-  </si>
-  <si>
-    <t>0.9034,0.0579,0.0148,0.0019</t>
-  </si>
-  <si>
-    <t>0.8441,0.0794,0.0513,0.0035</t>
-  </si>
-  <si>
-    <t>0.6923,0.2040,0.0912,0.0076</t>
-  </si>
-  <si>
-    <t>0.7780,0.1020,0.0768,0.0066</t>
-  </si>
-  <si>
-    <t>0.9483,0.0051,0.0462,0.0001</t>
-  </si>
-  <si>
-    <t>0.7444,0.0289,0.2038,0.0001</t>
-  </si>
-  <si>
-    <t>0.7129,0.0154,0.3743,0.0002</t>
-  </si>
-  <si>
-    <t>0.9505,0.0038,0.0371,0.0001</t>
-  </si>
-  <si>
-    <t>0.9452,0.0164,0.0336,0.0003</t>
-  </si>
-  <si>
-    <t>0.9690,0.0090,0.0141,0.0002</t>
-  </si>
-  <si>
-    <t>0.9365,0.0159,0.0477,0.0003</t>
-  </si>
-  <si>
-    <t>0.8738,0.0644,0.0537,0.0010</t>
-  </si>
-  <si>
-    <t>0.9305,0.0301,0.0224,0.0021</t>
-  </si>
-  <si>
-    <t>0.9630,0.0048,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.9783,0.0077,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.9192,0.0325,0.0278,0.0008</t>
-  </si>
-  <si>
-    <t>0.7354,0.1162,0.0616,0.0005</t>
-  </si>
-  <si>
-    <t>0.8252,0.1358,0.0363,0.0025</t>
-  </si>
-  <si>
-    <t>0.6797,0.3131,0.0659,0.0025</t>
-  </si>
-  <si>
-    <t>0.6028,0.3147,0.1381,0.0088</t>
-  </si>
-  <si>
-    <t>0.6619,0.3415,0.0584,0.0048</t>
-  </si>
-  <si>
-    <t>0.8283,0.1039,0.0460,0.0051</t>
-  </si>
-  <si>
-    <t>0.8193,0.1011,0.0309,0.0043</t>
-  </si>
-  <si>
-    <t>0.5689,0.2136,0.0884,0.0279</t>
-  </si>
-  <si>
-    <t>0.1184,0.5742,0.7436,0.0210</t>
-  </si>
-  <si>
-    <t>0.6543,0.1146,0.0378,0.0402</t>
-  </si>
-  <si>
-    <t>0.8380,0.0821,0.0370,0.0056</t>
-  </si>
-  <si>
-    <t>0.8082,0.1587,0.0498,0.0010</t>
-  </si>
-  <si>
-    <t>0.9295,0.0299,0.0166,0.0015</t>
-  </si>
-  <si>
-    <t>0.8369,0.0919,0.0708,0.0030</t>
-  </si>
-  <si>
-    <t>0.7424,0.2310,0.0585,0.0028</t>
-  </si>
-  <si>
-    <t>0.8770,0.0603,0.0617,0.0009</t>
-  </si>
-  <si>
-    <t>0.8820,0.1239,0.0276,0.0004</t>
-  </si>
-  <si>
-    <t>0.7790,0.1910,0.0238,0.0039</t>
-  </si>
-  <si>
-    <t>0.7348,0.2122,0.0325,0.0054</t>
-  </si>
-  <si>
-    <t>0.7386,0.2271,0.0668,0.0061</t>
-  </si>
-  <si>
-    <t>0.6814,0.1507,0.0557,0.0143</t>
-  </si>
-  <si>
-    <t>0.7896,0.0942,0.0282,0.0084</t>
-  </si>
-  <si>
-    <t>0.7224,0.1796,0.0484,0.0086</t>
-  </si>
-  <si>
-    <t>0.7258,0.2183,0.0960,0.0044</t>
-  </si>
-  <si>
-    <t>0.7926,0.1300,0.0361,0.0076</t>
-  </si>
-  <si>
-    <t>0.8303,0.1716,0.0330,0.0009</t>
-  </si>
-  <si>
-    <t>0.7070,0.2542,0.0541,0.0058</t>
-  </si>
-  <si>
-    <t>0.8007,0.1960,0.0500,0.0009</t>
-  </si>
-  <si>
-    <t>0.7977,0.0571,0.0576,0.0142</t>
-  </si>
-  <si>
-    <t>0.7712,0.0990,0.0355,0.0145</t>
-  </si>
-  <si>
-    <t>0.7700,0.1228,0.1177,0.0049</t>
-  </si>
-  <si>
-    <t>0.8852,0.0933,0.0296,0.0020</t>
-  </si>
-  <si>
-    <t>0.7084,0.1162,0.0960,0.0145</t>
-  </si>
-  <si>
-    <t>0.2188,0.0870,0.8408,0.0007</t>
-  </si>
-  <si>
-    <t>0.8037,0.1626,0.0406,0.0026</t>
-  </si>
-  <si>
-    <t>0.7859,0.0120,0.2936,0.0004</t>
-  </si>
-  <si>
-    <t>0.9822,0.0016,0.0154,0.0000</t>
-  </si>
-  <si>
-    <t>0.9453,0.0098,0.0537,0.0001</t>
-  </si>
-  <si>
-    <t>0.4618,0.0471,0.5048,0.0003</t>
-  </si>
-  <si>
-    <t>0.9514,0.0064,0.0462,0.0001</t>
-  </si>
-  <si>
-    <t>0.9244,0.0025,0.1013,0.0001</t>
-  </si>
-  <si>
-    <t>0.7769,0.0049,0.4057,0.0002</t>
-  </si>
-  <si>
-    <t>0.8489,0.0818,0.0695,0.0012</t>
-  </si>
-  <si>
-    <t>0.9115,0.0298,0.0540,0.0007</t>
-  </si>
-  <si>
-    <t>0.7997,0.1013,0.1261,0.0008</t>
-  </si>
-  <si>
-    <t>0.7113,0.2280,0.0717,0.0006</t>
-  </si>
-  <si>
-    <t>0.9309,0.0391,0.0316,0.0005</t>
-  </si>
-  <si>
-    <t>0.8577,0.0657,0.0748,0.0008</t>
-  </si>
-  <si>
-    <t>0.9571,0.0133,0.0238,0.0001</t>
-  </si>
-  <si>
-    <t>0.9550,0.0134,0.0255,0.0002</t>
-  </si>
-  <si>
-    <t>0.7492,0.1182,0.0594,0.0123</t>
-  </si>
-  <si>
-    <t>0.3227,0.6352,0.0687,0.0091</t>
-  </si>
-  <si>
-    <t>0.7696,0.2195,0.0567,0.0018</t>
-  </si>
-  <si>
-    <t>0.7597,0.1032,0.0335,0.0107</t>
-  </si>
-  <si>
-    <t>0.8649,0.0743,0.0274,0.0034</t>
-  </si>
-  <si>
-    <t>0.6929,0.3281,0.0593,0.0016</t>
-  </si>
-  <si>
-    <t>0.9623,0.0044,0.0233,0.0004</t>
-  </si>
-  <si>
-    <t>0.9617,0.0086,0.0222,0.0004</t>
-  </si>
-  <si>
-    <t>0.8438,0.1018,0.0752,0.0005</t>
-  </si>
-  <si>
-    <t>0.9683,0.0103,0.0115,0.0003</t>
-  </si>
-  <si>
-    <t>0.5766,0.0440,0.4840,0.0011</t>
-  </si>
-  <si>
-    <t>0.9776,0.0027,0.0147,0.0001</t>
-  </si>
-  <si>
-    <t>0.9618,0.0013,0.0341,0.0003</t>
-  </si>
-  <si>
-    <t>0.9820,0.0023,0.0094,0.0001</t>
-  </si>
-  <si>
-    <t>0.8881,0.0484,0.0453,0.0001</t>
-  </si>
-  <si>
-    <t>0.7780,0.0691,0.0723,0.0184</t>
-  </si>
-  <si>
-    <t>0.5727,0.2079,0.0597,0.0279</t>
-  </si>
-  <si>
-    <t>0.7984,0.1371,0.0477,0.0043</t>
-  </si>
-  <si>
-    <t>0.8232,0.0705,0.0917,0.0023</t>
-  </si>
-  <si>
-    <t>0.7205,0.0929,0.0473,0.0205</t>
-  </si>
-  <si>
-    <t>0.7760,0.0809,0.0598,0.0111</t>
-  </si>
-  <si>
-    <t>0.5980,0.3271,0.0900,0.0175</t>
-  </si>
-  <si>
-    <t>0.8079,0.0737,0.0399,0.0128</t>
-  </si>
-  <si>
-    <t>0.6620,0.1191,0.2922,0.0011</t>
-  </si>
-  <si>
-    <t>0.6598,0.2146,0.1340,0.0049</t>
-  </si>
-  <si>
-    <t>0.8701,0.0613,0.0480,0.0022</t>
-  </si>
-  <si>
-    <t>0.8892,0.0031,0.1585,0.0001</t>
-  </si>
-  <si>
-    <t>0.4349,0.1311,0.3860,0.0025</t>
-  </si>
-  <si>
-    <t>0.8978,0.0162,0.0932,0.0002</t>
-  </si>
-  <si>
-    <t>0.8001,0.0041,0.3505,0.0003</t>
-  </si>
-  <si>
-    <t>0.9331,0.0149,0.0467,0.0001</t>
-  </si>
-  <si>
-    <t>0.3958,0.0272,0.6694,0.0006</t>
-  </si>
-  <si>
-    <t>0.9665,0.0012,0.0402,0.0001</t>
-  </si>
-  <si>
-    <t>0.9490,0.0290,0.0141,0.0002</t>
-  </si>
-  <si>
-    <t>0.9105,0.0136,0.0760,0.0010</t>
-  </si>
-  <si>
-    <t>0.9682,0.0062,0.0185,0.0002</t>
-  </si>
-  <si>
-    <t>0.9346,0.0338,0.0247,0.0002</t>
-  </si>
-  <si>
-    <t>0.7099,0.1504,0.0326,0.0095</t>
-  </si>
-  <si>
-    <t>0.8313,0.0830,0.0627,0.0037</t>
-  </si>
-  <si>
-    <t>0.5547,0.3522,0.1043,0.0111</t>
-  </si>
-  <si>
-    <t>0.6234,0.1212,0.0533,0.0384</t>
-  </si>
-  <si>
-    <t>0.7264,0.0811,0.0455,0.0190</t>
-  </si>
-  <si>
-    <t>0.7402,0.0972,0.0291,0.0119</t>
-  </si>
-  <si>
-    <t>0.7335,0.0962,0.0662,0.0195</t>
-  </si>
-  <si>
-    <t>0.5790,0.2160,0.0767,0.0196</t>
-  </si>
-  <si>
-    <t>0.8934,0.0120,0.1200,0.0003</t>
-  </si>
-  <si>
-    <t>0.8858,0.0051,0.1605,0.0001</t>
-  </si>
-  <si>
-    <t>0.8331,0.0294,0.1153,0.0003</t>
-  </si>
-  <si>
-    <t>0.8607,0.0095,0.1667,0.0002</t>
-  </si>
-  <si>
-    <t>0.9429,0.0047,0.0645,0.0002</t>
-  </si>
-  <si>
-    <t>0.8522,0.0200,0.1445,0.0006</t>
-  </si>
-  <si>
-    <t>0.9743,0.0023,0.0187,0.0001</t>
-  </si>
-  <si>
-    <t>0.9680,0.0021,0.0259,0.0002</t>
-  </si>
-  <si>
-    <t>0.7763,0.0739,0.0571,0.0142</t>
-  </si>
-  <si>
-    <t>0.9662,0.0080,0.0146,0.0005</t>
-  </si>
-  <si>
-    <t>0.8927,0.0679,0.0300,0.0019</t>
-  </si>
-  <si>
-    <t>0.9090,0.0203,0.0367,0.0021</t>
-  </si>
-  <si>
-    <t>0.8430,0.0259,0.0302,0.0156</t>
-  </si>
-  <si>
-    <t>0.8836,0.0520,0.0566,0.0015</t>
+    <t>0.8376,0.0698,0.0722,0.0052</t>
+  </si>
+  <si>
+    <t>0.7100,0.1590,0.0747,0.0097</t>
+  </si>
+  <si>
+    <t>0.9057,0.0308,0.0452,0.0027</t>
+  </si>
+  <si>
+    <t>0.9114,0.0501,0.0230,0.0018</t>
+  </si>
+  <si>
+    <t>0.8377,0.0749,0.0185,0.0066</t>
+  </si>
+  <si>
+    <t>0.8138,0.1046,0.0265,0.0072</t>
+  </si>
+  <si>
+    <t>0.6956,0.2437,0.0303,0.0053</t>
+  </si>
+  <si>
+    <t>0.7685,0.0487,0.0339,0.0252</t>
+  </si>
+  <si>
+    <t>0.6731,0.1592,0.0478,0.0174</t>
+  </si>
+  <si>
+    <t>0.5336,0.2846,0.0629,0.0191</t>
+  </si>
+  <si>
+    <t>0.7984,0.1016,0.0439,0.0058</t>
+  </si>
+  <si>
+    <t>0.7656,0.0880,0.0348,0.0200</t>
+  </si>
+  <si>
+    <t>0.9592,0.0294,0.0101,0.0001</t>
+  </si>
+  <si>
+    <t>0.8591,0.0375,0.1012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9769,0.0103,0.0109,0.0001</t>
+  </si>
+  <si>
+    <t>0.6959,0.0243,0.3912,0.0004</t>
+  </si>
+  <si>
+    <t>0.6210,0.4861,0.0504,0.0009</t>
+  </si>
+  <si>
+    <t>0.0493,0.9692,0.0402,0.0004</t>
+  </si>
+  <si>
+    <t>0.1257,0.8996,0.1165,0.0011</t>
+  </si>
+  <si>
+    <t>0.5503,0.5448,0.0526,0.0021</t>
+  </si>
+  <si>
+    <t>0.2732,0.7933,0.1318,0.0043</t>
+  </si>
+  <si>
+    <t>0.0956,0.9213,0.0829,0.0007</t>
+  </si>
+  <si>
+    <t>0.9629,0.0054,0.0232,0.0001</t>
+  </si>
+  <si>
+    <t>0.9537,0.0126,0.0340,0.0002</t>
+  </si>
+  <si>
+    <t>0.9568,0.0029,0.0388,0.0002</t>
+  </si>
+  <si>
+    <t>0.9699,0.0027,0.0217,0.0001</t>
+  </si>
+  <si>
+    <t>0.8859,0.0117,0.1356,0.0003</t>
+  </si>
+  <si>
+    <t>0.9263,0.0076,0.0833,0.0002</t>
+  </si>
+  <si>
+    <t>0.7822,0.0224,0.3008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9023,0.0991,0.0255,0.0005</t>
+  </si>
+  <si>
+    <t>0.7528,0.1706,0.0994,0.0028</t>
+  </si>
+  <si>
+    <t>0.2628,0.0694,0.8156,0.0020</t>
+  </si>
+  <si>
+    <t>0.6391,0.2986,0.0956,0.0008</t>
+  </si>
+  <si>
+    <t>0.9055,0.0422,0.0348,0.0013</t>
+  </si>
+  <si>
+    <t>0.7391,0.2218,0.0600,0.0015</t>
+  </si>
+  <si>
+    <t>0.4108,0.5600,0.1127,0.0112</t>
+  </si>
+  <si>
+    <t>0.8821,0.1569,0.0178,0.0005</t>
+  </si>
+  <si>
+    <t>0.6838,0.1768,0.0457,0.0006</t>
+  </si>
+  <si>
+    <t>0.9410,0.0041,0.0445,0.0005</t>
+  </si>
+  <si>
+    <t>0.9605,0.0007,0.0471,0.0000</t>
+  </si>
+  <si>
+    <t>0.9226,0.0168,0.0522,0.0009</t>
+  </si>
+  <si>
+    <t>0.9269,0.0130,0.0478,0.0001</t>
+  </si>
+  <si>
+    <t>0.9357,0.0192,0.0253,0.0005</t>
+  </si>
+  <si>
+    <t>0.9816,0.0016,0.0145,0.0001</t>
+  </si>
+  <si>
+    <t>0.8481,0.1775,0.0203,0.0012</t>
+  </si>
+  <si>
+    <t>0.7909,0.3315,0.0138,0.0001</t>
+  </si>
+  <si>
+    <t>0.0548,0.9608,0.0354,0.0004</t>
+  </si>
+  <si>
+    <t>0.3630,0.7339,0.0828,0.0004</t>
+  </si>
+  <si>
+    <t>0.6201,0.1676,0.1089,0.0005</t>
+  </si>
+  <si>
+    <t>0.5031,0.0261,0.5860,0.0006</t>
+  </si>
+  <si>
+    <t>0.9052,0.0109,0.0871,0.0003</t>
+  </si>
+  <si>
+    <t>0.9304,0.0096,0.0616,0.0002</t>
+  </si>
+  <si>
+    <t>0.6273,0.0319,0.4172,0.0005</t>
+  </si>
+  <si>
+    <t>0.8859,0.0038,0.2037,0.0001</t>
+  </si>
+  <si>
+    <t>0.7573,0.2143,0.0267,0.0027</t>
+  </si>
+  <si>
+    <t>0.8750,0.0843,0.0210,0.0028</t>
+  </si>
+  <si>
+    <t>0.5416,0.2285,0.0824,0.0250</t>
+  </si>
+  <si>
+    <t>0.2314,0.2331,0.7756,0.0035</t>
+  </si>
+  <si>
+    <t>0.7298,0.1494,0.0628,0.0167</t>
+  </si>
+  <si>
+    <t>0.5704,0.2565,0.0844,0.0177</t>
+  </si>
+  <si>
+    <t>0.6586,0.3047,0.0998,0.0053</t>
+  </si>
+  <si>
+    <t>0.1333,0.6332,0.3533,0.0001</t>
+  </si>
+  <si>
+    <t>0.6824,0.0169,0.4234,0.0004</t>
+  </si>
+  <si>
+    <t>0.4376,0.0332,0.6976,0.0003</t>
+  </si>
+  <si>
+    <t>0.7233,0.0530,0.2267,0.0004</t>
+  </si>
+  <si>
+    <t>0.6445,0.0050,0.5714,0.0004</t>
+  </si>
+  <si>
+    <t>0.8426,0.2358,0.0115,0.0003</t>
+  </si>
+  <si>
+    <t>0.0170,0.9860,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.8716,0.0923,0.0319,0.0010</t>
+  </si>
+  <si>
+    <t>0.9284,0.0337,0.0176,0.0013</t>
+  </si>
+  <si>
+    <t>0.3331,0.2055,0.6522,0.0014</t>
+  </si>
+  <si>
+    <t>0.1093,0.6176,0.5348,0.0002</t>
+  </si>
+  <si>
+    <t>0.9051,0.0219,0.0376,0.0001</t>
+  </si>
+  <si>
+    <t>0.4470,0.5897,0.0134,0.0001</t>
+  </si>
+  <si>
+    <t>0.7240,0.1670,0.0436,0.0001</t>
+  </si>
+  <si>
+    <t>0.8780,0.0280,0.0433,0.0058</t>
+  </si>
+  <si>
+    <t>0.9065,0.0384,0.0180,0.0042</t>
+  </si>
+  <si>
+    <t>0.9149,0.0816,0.0166,0.0013</t>
+  </si>
+  <si>
+    <t>0.9707,0.0148,0.0063,0.0007</t>
+  </si>
+  <si>
+    <t>0.8086,0.0843,0.0636,0.0069</t>
+  </si>
+  <si>
+    <t>0.9415,0.0425,0.0142,0.0005</t>
+  </si>
+  <si>
+    <t>0.5247,0.2140,0.1397,0.0002</t>
+  </si>
+  <si>
+    <t>0.6611,0.0124,0.4865,0.0006</t>
+  </si>
+  <si>
+    <t>0.8900,0.0216,0.1179,0.0002</t>
+  </si>
+  <si>
+    <t>0.9472,0.0035,0.0563,0.0002</t>
+  </si>
+  <si>
+    <t>0.2515,0.5538,0.1567,0.0001</t>
+  </si>
+  <si>
+    <t>0.9091,0.0088,0.0828,0.0002</t>
+  </si>
+  <si>
+    <t>0.9446,0.0287,0.0157,0.0010</t>
+  </si>
+  <si>
+    <t>0.7338,0.2136,0.0556,0.0056</t>
+  </si>
+  <si>
+    <t>0.7332,0.1620,0.0824,0.0097</t>
+  </si>
+  <si>
+    <t>0.8328,0.0937,0.0477,0.0049</t>
+  </si>
+  <si>
+    <t>0.6293,0.1263,0.0574,0.0312</t>
+  </si>
+  <si>
+    <t>0.6548,0.1068,0.0323,0.0309</t>
+  </si>
+  <si>
+    <t>0.7161,0.1352,0.0592,0.0118</t>
+  </si>
+  <si>
+    <t>0.6505,0.2126,0.0664,0.0151</t>
+  </si>
+  <si>
+    <t>0.7695,0.1155,0.0444,0.0082</t>
+  </si>
+  <si>
+    <t>0.7479,0.1469,0.0406,0.0074</t>
+  </si>
+  <si>
+    <t>0.9089,0.0215,0.0151,0.0055</t>
+  </si>
+  <si>
+    <t>0.8767,0.0514,0.0322,0.0061</t>
+  </si>
+  <si>
+    <t>0.7259,0.1762,0.0479,0.0064</t>
+  </si>
+  <si>
+    <t>0.8490,0.0880,0.0386,0.0053</t>
+  </si>
+  <si>
+    <t>0.7090,0.1041,0.0816,0.0260</t>
+  </si>
+  <si>
+    <t>0.7678,0.1477,0.0403,0.0064</t>
+  </si>
+  <si>
+    <t>0.2218,0.0632,0.8458,0.0019</t>
+  </si>
+  <si>
+    <t>0.6822,0.0375,0.4185,0.0010</t>
+  </si>
+  <si>
+    <t>0.9795,0.0051,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.9629,0.0013,0.0482,0.0000</t>
+  </si>
+  <si>
+    <t>0.6058,0.4385,0.0655,0.0008</t>
+  </si>
+  <si>
+    <t>0.4369,0.5341,0.1845,0.0018</t>
+  </si>
+  <si>
+    <t>0.5335,0.4279,0.0950,0.0017</t>
+  </si>
+  <si>
+    <t>0.3743,0.6583,0.1426,0.0054</t>
+  </si>
+  <si>
+    <t>0.3565,0.7230,0.0655,0.0021</t>
+  </si>
+  <si>
+    <t>0.1083,0.9194,0.0673,0.0006</t>
+  </si>
+  <si>
+    <t>0.6187,0.4067,0.1033,0.0037</t>
+  </si>
+  <si>
+    <t>0.9619,0.0216,0.0098,0.0003</t>
+  </si>
+  <si>
+    <t>0.9565,0.0065,0.0358,0.0001</t>
+  </si>
+  <si>
+    <t>0.9177,0.0540,0.0330,0.0005</t>
+  </si>
+  <si>
+    <t>0.9798,0.0028,0.0118,0.0001</t>
+  </si>
+  <si>
+    <t>0.9258,0.0357,0.0304,0.0006</t>
+  </si>
+  <si>
+    <t>0.5120,0.5742,0.0750,0.0004</t>
+  </si>
+  <si>
+    <t>0.5474,0.5899,0.0515,0.0019</t>
+  </si>
+  <si>
+    <t>0.1369,0.9091,0.0600,0.0006</t>
+  </si>
+  <si>
+    <t>0.1147,0.8316,0.2974,0.0007</t>
+  </si>
+  <si>
+    <t>0.7366,0.2988,0.0475,0.0011</t>
+  </si>
+  <si>
+    <t>0.8211,0.1649,0.0423,0.0011</t>
+  </si>
+  <si>
+    <t>0.8130,0.1377,0.0527,0.0042</t>
+  </si>
+  <si>
+    <t>0.8729,0.0956,0.0251,0.0021</t>
+  </si>
+  <si>
+    <t>0.7542,0.0962,0.0883,0.0121</t>
+  </si>
+  <si>
+    <t>0.7889,0.1777,0.0310,0.0032</t>
+  </si>
+  <si>
+    <t>0.6310,0.3154,0.0718,0.0062</t>
+  </si>
+  <si>
+    <t>0.9062,0.0334,0.0271,0.0044</t>
+  </si>
+  <si>
+    <t>0.7098,0.2663,0.0510,0.0027</t>
+  </si>
+  <si>
+    <t>0.7359,0.1287,0.0500,0.0125</t>
+  </si>
+  <si>
+    <t>0.6992,0.1776,0.0691,0.0088</t>
+  </si>
+  <si>
+    <t>0.4947,0.0730,0.3471,0.0003</t>
+  </si>
+  <si>
+    <t>0.8043,0.0550,0.1152,0.0003</t>
+  </si>
+  <si>
+    <t>0.7846,0.0086,0.3529,0.0003</t>
+  </si>
+  <si>
+    <t>0.7610,0.0171,0.2815,0.0005</t>
+  </si>
+  <si>
+    <t>0.9402,0.0059,0.0692,0.0001</t>
+  </si>
+  <si>
+    <t>0.9345,0.0245,0.0364,0.0004</t>
+  </si>
+  <si>
+    <t>0.9066,0.0093,0.1057,0.0002</t>
+  </si>
+  <si>
+    <t>0.8962,0.0506,0.0362,0.0014</t>
+  </si>
+  <si>
+    <t>0.9358,0.0459,0.0131,0.0014</t>
+  </si>
+  <si>
+    <t>0.8086,0.0823,0.0327,0.0161</t>
+  </si>
+  <si>
+    <t>0.9298,0.0328,0.0081,0.0019</t>
+  </si>
+  <si>
+    <t>0.7336,0.1022,0.0587,0.0318</t>
+  </si>
+  <si>
+    <t>0.5904,0.1032,0.3479,0.0013</t>
+  </si>
+  <si>
+    <t>0.7500,0.1918,0.0834,0.0042</t>
+  </si>
+  <si>
+    <t>0.7748,0.2065,0.0333,0.0031</t>
+  </si>
+  <si>
+    <t>0.7073,0.1692,0.0870,0.0119</t>
+  </si>
+  <si>
+    <t>0.5773,0.2796,0.0840,0.0123</t>
+  </si>
+  <si>
+    <t>0.6852,0.1734,0.1840,0.0061</t>
+  </si>
+  <si>
+    <t>0.7635,0.2073,0.0403,0.0036</t>
+  </si>
+  <si>
+    <t>0.6475,0.1194,0.0506,0.0284</t>
+  </si>
+  <si>
+    <t>0.2307,0.1685,0.7828,0.0089</t>
+  </si>
+  <si>
+    <t>0.9321,0.0201,0.0091,0.0042</t>
+  </si>
+  <si>
+    <t>0.5983,0.2922,0.0812,0.0117</t>
+  </si>
+  <si>
+    <t>0.7034,0.3839,0.0390,0.0010</t>
+  </si>
+  <si>
+    <t>0.9468,0.0319,0.0133,0.0004</t>
+  </si>
+  <si>
+    <t>0.9486,0.0238,0.0158,0.0005</t>
+  </si>
+  <si>
+    <t>0.9177,0.0295,0.0322,0.0017</t>
+  </si>
+  <si>
+    <t>0.8474,0.1888,0.0219,0.0007</t>
+  </si>
+  <si>
+    <t>0.9598,0.0186,0.0106,0.0004</t>
+  </si>
+  <si>
+    <t>0.6845,0.1979,0.0492,0.0127</t>
+  </si>
+  <si>
+    <t>0.7989,0.0841,0.0446,0.0080</t>
+  </si>
+  <si>
+    <t>0.8941,0.0523,0.0267,0.0039</t>
+  </si>
+  <si>
+    <t>0.8209,0.0824,0.0405,0.0050</t>
+  </si>
+  <si>
+    <t>0.7057,0.2451,0.0545,0.0071</t>
+  </si>
+  <si>
+    <t>0.7297,0.2063,0.0611,0.0093</t>
+  </si>
+  <si>
+    <t>0.6830,0.1085,0.0449,0.0278</t>
+  </si>
+  <si>
+    <t>0.8951,0.0609,0.0270,0.0025</t>
+  </si>
+  <si>
+    <t>0.6840,0.3235,0.0573,0.0043</t>
+  </si>
+  <si>
+    <t>0.7879,0.1152,0.0286,0.0045</t>
+  </si>
+  <si>
+    <t>0.6398,0.3829,0.0837,0.0026</t>
+  </si>
+  <si>
+    <t>0.8931,0.0591,0.0108,0.0019</t>
+  </si>
+  <si>
+    <t>0.6657,0.2477,0.0926,0.0117</t>
+  </si>
+  <si>
+    <t>0.6268,0.3285,0.1188,0.0026</t>
+  </si>
+  <si>
+    <t>0.8620,0.0841,0.0245,0.0026</t>
+  </si>
+  <si>
+    <t>0.7811,0.1028,0.0785,0.0108</t>
+  </si>
+  <si>
+    <t>0.0671,0.1281,0.9484,0.0018</t>
+  </si>
+  <si>
+    <t>0.6226,0.2765,0.1498,0.0109</t>
+  </si>
+  <si>
+    <t>0.8014,0.0132,0.2338,0.0015</t>
+  </si>
+  <si>
+    <t>0.9682,0.0020,0.0335,0.0001</t>
+  </si>
+  <si>
+    <t>0.9603,0.0148,0.0188,0.0001</t>
+  </si>
+  <si>
+    <t>0.0979,0.3082,0.7750,0.0015</t>
+  </si>
+  <si>
+    <t>0.9568,0.0032,0.0578,0.0001</t>
+  </si>
+  <si>
+    <t>0.9527,0.0021,0.0599,0.0001</t>
+  </si>
+  <si>
+    <t>0.8110,0.0139,0.2348,0.0002</t>
+  </si>
+  <si>
+    <t>0.8586,0.0553,0.0911,0.0003</t>
+  </si>
+  <si>
+    <t>0.9501,0.0097,0.0317,0.0003</t>
+  </si>
+  <si>
+    <t>0.7833,0.1069,0.1442,0.0007</t>
+  </si>
+  <si>
+    <t>0.9417,0.0475,0.0153,0.0002</t>
+  </si>
+  <si>
+    <t>0.9308,0.0271,0.0356,0.0004</t>
+  </si>
+  <si>
+    <t>0.8743,0.0861,0.0513,0.0003</t>
+  </si>
+  <si>
+    <t>0.9724,0.0142,0.0090,0.0001</t>
+  </si>
+  <si>
+    <t>0.9680,0.0077,0.0184,0.0001</t>
+  </si>
+  <si>
+    <t>0.5936,0.1147,0.0672,0.0424</t>
+  </si>
+  <si>
+    <t>0.6397,0.3242,0.0549,0.0037</t>
+  </si>
+  <si>
+    <t>0.8771,0.0633,0.0359,0.0026</t>
+  </si>
+  <si>
+    <t>0.6929,0.1345,0.0737,0.0218</t>
+  </si>
+  <si>
+    <t>0.5471,0.3338,0.1210,0.0153</t>
+  </si>
+  <si>
+    <t>0.9724,0.0124,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.9717,0.0086,0.0127,0.0002</t>
+  </si>
+  <si>
+    <t>0.7854,0.1818,0.0733,0.0014</t>
+  </si>
+  <si>
+    <t>0.9722,0.0048,0.0191,0.0001</t>
+  </si>
+  <si>
+    <t>0.9336,0.0060,0.0707,0.0002</t>
+  </si>
+  <si>
+    <t>0.9139,0.0287,0.0499,0.0002</t>
+  </si>
+  <si>
+    <t>0.9719,0.0021,0.0272,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0005,0.0075,0.0000</t>
+  </si>
+  <si>
+    <t>0.9643,0.0022,0.0303,0.0001</t>
+  </si>
+  <si>
+    <t>0.9572,0.0137,0.0184,0.0001</t>
+  </si>
+  <si>
+    <t>0.7252,0.1783,0.0701,0.0078</t>
+  </si>
+  <si>
+    <t>0.7306,0.2117,0.0478,0.0072</t>
+  </si>
+  <si>
+    <t>0.7086,0.0908,0.0369,0.0323</t>
+  </si>
+  <si>
+    <t>0.7911,0.0872,0.0422,0.0085</t>
+  </si>
+  <si>
+    <t>0.6628,0.2602,0.0820,0.0123</t>
+  </si>
+  <si>
+    <t>0.8331,0.1368,0.0215,0.0026</t>
+  </si>
+  <si>
+    <t>0.5467,0.3386,0.0658,0.0128</t>
+  </si>
+  <si>
+    <t>0.6780,0.2906,0.0608,0.0060</t>
+  </si>
+  <si>
+    <t>0.8552,0.0875,0.0242,0.0028</t>
+  </si>
+  <si>
+    <t>0.9076,0.0487,0.0289,0.0013</t>
+  </si>
+  <si>
+    <t>0.7864,0.1433,0.0852,0.0023</t>
+  </si>
+  <si>
+    <t>0.8954,0.0043,0.1205,0.0003</t>
+  </si>
+  <si>
+    <t>0.3884,0.0054,0.8184,0.0005</t>
+  </si>
+  <si>
+    <t>0.9440,0.0042,0.0602,0.0002</t>
+  </si>
+  <si>
+    <t>0.7781,0.0074,0.3434,0.0003</t>
+  </si>
+  <si>
+    <t>0.9802,0.0037,0.0115,0.0000</t>
+  </si>
+  <si>
+    <t>0.5024,0.0108,0.6908,0.0006</t>
+  </si>
+  <si>
+    <t>0.8781,0.0251,0.0719,0.0002</t>
+  </si>
+  <si>
+    <t>0.8678,0.0435,0.0928,0.0004</t>
+  </si>
+  <si>
+    <t>0.9543,0.0037,0.0320,0.0007</t>
+  </si>
+  <si>
+    <t>0.9313,0.0187,0.0538,0.0004</t>
+  </si>
+  <si>
+    <t>0.8880,0.0522,0.0489,0.0006</t>
+  </si>
+  <si>
+    <t>0.7397,0.0717,0.0257,0.0270</t>
+  </si>
+  <si>
+    <t>0.7425,0.1050,0.0509,0.0127</t>
+  </si>
+  <si>
+    <t>0.8476,0.0593,0.0256,0.0070</t>
+  </si>
+  <si>
+    <t>0.7027,0.2431,0.0485,0.0048</t>
+  </si>
+  <si>
+    <t>0.6515,0.0795,0.0295,0.0357</t>
+  </si>
+  <si>
+    <t>0.6361,0.2819,0.0616,0.0102</t>
+  </si>
+  <si>
+    <t>0.7952,0.1179,0.0270,0.0050</t>
+  </si>
+  <si>
+    <t>0.7208,0.0600,0.0246,0.0325</t>
+  </si>
+  <si>
+    <t>0.6689,0.1060,0.1497,0.0003</t>
+  </si>
+  <si>
+    <t>0.8681,0.0102,0.1684,0.0003</t>
+  </si>
+  <si>
+    <t>0.7640,0.0304,0.1902,0.0007</t>
+  </si>
+  <si>
+    <t>0.9261,0.0225,0.0426,0.0004</t>
+  </si>
+  <si>
+    <t>0.8848,0.0034,0.1601,0.0002</t>
+  </si>
+  <si>
+    <t>0.9533,0.0067,0.0318,0.0003</t>
+  </si>
+  <si>
+    <t>0.9566,0.0090,0.0258,0.0002</t>
+  </si>
+  <si>
+    <t>0.9788,0.0024,0.0106,0.0003</t>
+  </si>
+  <si>
+    <t>0.8807,0.0370,0.0219,0.0054</t>
+  </si>
+  <si>
+    <t>0.9207,0.0186,0.0168,0.0052</t>
+  </si>
+  <si>
+    <t>0.8699,0.0405,0.0632,0.0039</t>
+  </si>
+  <si>
+    <t>0.8907,0.0384,0.0429,0.0022</t>
+  </si>
+  <si>
+    <t>0.9214,0.0240,0.0212,0.0032</t>
+  </si>
+  <si>
+    <t>0.8703,0.1179,0.0314,0.0008</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8376,0.0698,0.0722,0.0052</t>
-  </si>
-  <si>
-    <t>0.7100,0.1590,0.0747,0.0097</t>
-  </si>
-  <si>
-    <t>0.9057,0.0308,0.0452,0.0027</t>
-  </si>
-  <si>
-    <t>0.9114,0.0501,0.0230,0.0018</t>
-  </si>
-  <si>
-    <t>0.8377,0.0749,0.0185,0.0066</t>
-  </si>
-  <si>
-    <t>0.8138,0.1046,0.0265,0.0072</t>
-  </si>
-  <si>
-    <t>0.6956,0.2437,0.0303,0.0053</t>
-  </si>
-  <si>
-    <t>0.7685,0.0487,0.0339,0.0252</t>
-  </si>
-  <si>
-    <t>0.6731,0.1592,0.0478,0.0174</t>
-  </si>
-  <si>
-    <t>0.5336,0.2846,0.0629,0.0191</t>
-  </si>
-  <si>
-    <t>0.7984,0.1016,0.0439,0.0058</t>
-  </si>
-  <si>
-    <t>0.7656,0.0880,0.0348,0.0200</t>
-  </si>
-  <si>
-    <t>0.9592,0.0294,0.0101,0.0001</t>
-  </si>
-  <si>
-    <t>0.8591,0.0375,0.1012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9769,0.0103,0.0109,0.0001</t>
-  </si>
-  <si>
-    <t>0.6959,0.0243,0.3912,0.0004</t>
-  </si>
-  <si>
-    <t>0.6210,0.4861,0.0504,0.0009</t>
-  </si>
-  <si>
-    <t>0.0493,0.9692,0.0402,0.0004</t>
-  </si>
-  <si>
-    <t>0.1257,0.8996,0.1165,0.0011</t>
-  </si>
-  <si>
-    <t>0.5503,0.5448,0.0526,0.0021</t>
-  </si>
-  <si>
-    <t>0.2732,0.7933,0.1318,0.0043</t>
-  </si>
-  <si>
-    <t>0.0956,0.9213,0.0829,0.0007</t>
-  </si>
-  <si>
-    <t>0.9629,0.0054,0.0232,0.0001</t>
-  </si>
-  <si>
-    <t>0.9537,0.0126,0.0340,0.0002</t>
-  </si>
-  <si>
-    <t>0.9568,0.0029,0.0388,0.0002</t>
-  </si>
-  <si>
-    <t>0.9699,0.0027,0.0217,0.0001</t>
-  </si>
-  <si>
-    <t>0.8859,0.0117,0.1356,0.0003</t>
-  </si>
-  <si>
-    <t>0.9263,0.0076,0.0833,0.0002</t>
-  </si>
-  <si>
-    <t>0.7822,0.0224,0.3008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9023,0.0991,0.0255,0.0005</t>
-  </si>
-  <si>
-    <t>0.7528,0.1706,0.0994,0.0028</t>
-  </si>
-  <si>
-    <t>0.2628,0.0694,0.8156,0.0020</t>
-  </si>
-  <si>
-    <t>0.6391,0.2986,0.0956,0.0008</t>
-  </si>
-  <si>
-    <t>0.9055,0.0422,0.0348,0.0013</t>
-  </si>
-  <si>
-    <t>0.7391,0.2218,0.0600,0.0015</t>
-  </si>
-  <si>
-    <t>0.4108,0.5600,0.1127,0.0112</t>
-  </si>
-  <si>
-    <t>0.8821,0.1569,0.0178,0.0005</t>
-  </si>
-  <si>
-    <t>0.6838,0.1768,0.0457,0.0006</t>
-  </si>
-  <si>
-    <t>0.9410,0.0041,0.0445,0.0005</t>
-  </si>
-  <si>
-    <t>0.9605,0.0007,0.0471,0.0000</t>
-  </si>
-  <si>
-    <t>0.9226,0.0168,0.0522,0.0009</t>
-  </si>
-  <si>
-    <t>0.9269,0.0130,0.0478,0.0001</t>
-  </si>
-  <si>
-    <t>0.9357,0.0192,0.0253,0.0005</t>
-  </si>
-  <si>
-    <t>0.9816,0.0016,0.0145,0.0001</t>
-  </si>
-  <si>
-    <t>0.8481,0.1775,0.0203,0.0012</t>
-  </si>
-  <si>
-    <t>0.7909,0.3315,0.0138,0.0001</t>
-  </si>
-  <si>
-    <t>0.0548,0.9608,0.0354,0.0004</t>
-  </si>
-  <si>
-    <t>0.3630,0.7339,0.0828,0.0004</t>
-  </si>
-  <si>
-    <t>0.6201,0.1676,0.1089,0.0005</t>
-  </si>
-  <si>
-    <t>0.5031,0.0261,0.5860,0.0006</t>
-  </si>
-  <si>
-    <t>0.9052,0.0109,0.0871,0.0003</t>
-  </si>
-  <si>
-    <t>0.9304,0.0096,0.0616,0.0002</t>
-  </si>
-  <si>
-    <t>0.6273,0.0319,0.4172,0.0005</t>
-  </si>
-  <si>
-    <t>0.8859,0.0038,0.2037,0.0001</t>
-  </si>
-  <si>
-    <t>0.7573,0.2143,0.0267,0.0027</t>
-  </si>
-  <si>
-    <t>0.8750,0.0843,0.0210,0.0028</t>
-  </si>
-  <si>
-    <t>0.5416,0.2285,0.0824,0.0250</t>
-  </si>
-  <si>
-    <t>0.2314,0.2331,0.7756,0.0035</t>
-  </si>
-  <si>
-    <t>0.7298,0.1494,0.0628,0.0167</t>
-  </si>
-  <si>
-    <t>0.5704,0.2565,0.0844,0.0177</t>
-  </si>
-  <si>
-    <t>0.6586,0.3047,0.0998,0.0053</t>
-  </si>
-  <si>
-    <t>0.1333,0.6332,0.3533,0.0001</t>
-  </si>
-  <si>
-    <t>0.6824,0.0169,0.4234,0.0004</t>
-  </si>
-  <si>
-    <t>0.4376,0.0332,0.6976,0.0003</t>
-  </si>
-  <si>
-    <t>0.7233,0.0530,0.2267,0.0004</t>
-  </si>
-  <si>
-    <t>0.6445,0.0050,0.5714,0.0004</t>
-  </si>
-  <si>
-    <t>0.8426,0.2358,0.0115,0.0003</t>
-  </si>
-  <si>
-    <t>0.0170,0.9860,0.0113,0.0002</t>
-  </si>
-  <si>
-    <t>0.8716,0.0923,0.0319,0.0010</t>
-  </si>
-  <si>
-    <t>0.9284,0.0337,0.0176,0.0013</t>
-  </si>
-  <si>
-    <t>0.3331,0.2055,0.6522,0.0014</t>
-  </si>
-  <si>
-    <t>0.1093,0.6176,0.5348,0.0002</t>
-  </si>
-  <si>
-    <t>0.9051,0.0219,0.0376,0.0001</t>
-  </si>
-  <si>
-    <t>0.4470,0.5897,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.7240,0.1670,0.0436,0.0001</t>
-  </si>
-  <si>
-    <t>0.8780,0.0280,0.0433,0.0058</t>
-  </si>
-  <si>
-    <t>0.9065,0.0384,0.0180,0.0042</t>
-  </si>
-  <si>
-    <t>0.9149,0.0816,0.0166,0.0013</t>
-  </si>
-  <si>
-    <t>0.9707,0.0148,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.8086,0.0843,0.0636,0.0069</t>
-  </si>
-  <si>
-    <t>0.9415,0.0425,0.0142,0.0005</t>
-  </si>
-  <si>
-    <t>0.5247,0.2140,0.1397,0.0002</t>
-  </si>
-  <si>
-    <t>0.6611,0.0124,0.4865,0.0006</t>
-  </si>
-  <si>
-    <t>0.8900,0.0216,0.1179,0.0002</t>
-  </si>
-  <si>
-    <t>0.9472,0.0035,0.0563,0.0002</t>
-  </si>
-  <si>
-    <t>0.2515,0.5538,0.1567,0.0001</t>
-  </si>
-  <si>
-    <t>0.9091,0.0088,0.0828,0.0002</t>
-  </si>
-  <si>
-    <t>0.9446,0.0287,0.0157,0.0010</t>
-  </si>
-  <si>
-    <t>0.7338,0.2136,0.0556,0.0056</t>
-  </si>
-  <si>
-    <t>0.7332,0.1620,0.0824,0.0097</t>
-  </si>
-  <si>
-    <t>0.8328,0.0937,0.0477,0.0049</t>
-  </si>
-  <si>
-    <t>0.6293,0.1263,0.0574,0.0312</t>
-  </si>
-  <si>
-    <t>0.6548,0.1068,0.0323,0.0309</t>
-  </si>
-  <si>
-    <t>0.7161,0.1352,0.0592,0.0118</t>
-  </si>
-  <si>
-    <t>0.6505,0.2126,0.0664,0.0151</t>
-  </si>
-  <si>
-    <t>0.7695,0.1155,0.0444,0.0082</t>
-  </si>
-  <si>
-    <t>0.7479,0.1469,0.0406,0.0074</t>
-  </si>
-  <si>
-    <t>0.9089,0.0215,0.0151,0.0055</t>
-  </si>
-  <si>
-    <t>0.8767,0.0514,0.0322,0.0061</t>
-  </si>
-  <si>
-    <t>0.7259,0.1762,0.0479,0.0064</t>
-  </si>
-  <si>
-    <t>0.8490,0.0880,0.0386,0.0053</t>
-  </si>
-  <si>
-    <t>0.7090,0.1041,0.0816,0.0260</t>
-  </si>
-  <si>
-    <t>0.7678,0.1477,0.0403,0.0064</t>
-  </si>
-  <si>
-    <t>0.2218,0.0632,0.8458,0.0019</t>
-  </si>
-  <si>
-    <t>0.6822,0.0375,0.4185,0.0010</t>
-  </si>
-  <si>
-    <t>0.9795,0.0051,0.0102,0.0001</t>
-  </si>
-  <si>
-    <t>0.9629,0.0013,0.0482,0.0000</t>
-  </si>
-  <si>
-    <t>0.6058,0.4385,0.0655,0.0008</t>
-  </si>
-  <si>
-    <t>0.4369,0.5341,0.1845,0.0018</t>
-  </si>
-  <si>
-    <t>0.5335,0.4279,0.0950,0.0017</t>
-  </si>
-  <si>
-    <t>0.3743,0.6583,0.1426,0.0054</t>
-  </si>
-  <si>
-    <t>0.3565,0.7230,0.0655,0.0021</t>
-  </si>
-  <si>
-    <t>0.1083,0.9194,0.0673,0.0006</t>
-  </si>
-  <si>
-    <t>0.6187,0.4067,0.1033,0.0037</t>
-  </si>
-  <si>
-    <t>0.9619,0.0216,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.9565,0.0065,0.0358,0.0001</t>
-  </si>
-  <si>
-    <t>0.9177,0.0540,0.0330,0.0005</t>
-  </si>
-  <si>
-    <t>0.9798,0.0028,0.0118,0.0001</t>
-  </si>
-  <si>
-    <t>0.9258,0.0357,0.0304,0.0006</t>
-  </si>
-  <si>
-    <t>0.5120,0.5742,0.0750,0.0004</t>
-  </si>
-  <si>
-    <t>0.5474,0.5899,0.0515,0.0019</t>
-  </si>
-  <si>
-    <t>0.1369,0.9091,0.0600,0.0006</t>
-  </si>
-  <si>
-    <t>0.1147,0.8316,0.2974,0.0007</t>
-  </si>
-  <si>
-    <t>0.7366,0.2988,0.0475,0.0011</t>
-  </si>
-  <si>
-    <t>0.8211,0.1649,0.0423,0.0011</t>
-  </si>
-  <si>
-    <t>0.8130,0.1377,0.0527,0.0042</t>
-  </si>
-  <si>
-    <t>0.8729,0.0956,0.0251,0.0021</t>
-  </si>
-  <si>
-    <t>0.7542,0.0962,0.0883,0.0121</t>
-  </si>
-  <si>
-    <t>0.7889,0.1777,0.0310,0.0032</t>
-  </si>
-  <si>
-    <t>0.6310,0.3154,0.0718,0.0062</t>
-  </si>
-  <si>
-    <t>0.9062,0.0334,0.0271,0.0044</t>
-  </si>
-  <si>
-    <t>0.7098,0.2663,0.0510,0.0027</t>
-  </si>
-  <si>
-    <t>0.7359,0.1287,0.0500,0.0125</t>
-  </si>
-  <si>
-    <t>0.6992,0.1776,0.0691,0.0088</t>
-  </si>
-  <si>
-    <t>0.4947,0.0730,0.3471,0.0003</t>
-  </si>
-  <si>
-    <t>0.8043,0.0550,0.1152,0.0003</t>
-  </si>
-  <si>
-    <t>0.7846,0.0086,0.3529,0.0003</t>
-  </si>
-  <si>
-    <t>0.7610,0.0171,0.2815,0.0005</t>
-  </si>
-  <si>
-    <t>0.9402,0.0059,0.0692,0.0001</t>
-  </si>
-  <si>
-    <t>0.9345,0.0245,0.0364,0.0004</t>
-  </si>
-  <si>
-    <t>0.9066,0.0093,0.1057,0.0002</t>
-  </si>
-  <si>
-    <t>0.8962,0.0506,0.0362,0.0014</t>
-  </si>
-  <si>
-    <t>0.9358,0.0459,0.0131,0.0014</t>
-  </si>
-  <si>
-    <t>0.8086,0.0823,0.0327,0.0161</t>
-  </si>
-  <si>
-    <t>0.9298,0.0328,0.0081,0.0019</t>
-  </si>
-  <si>
-    <t>0.7336,0.1022,0.0587,0.0318</t>
-  </si>
-  <si>
-    <t>0.5904,0.1032,0.3479,0.0013</t>
-  </si>
-  <si>
-    <t>0.7500,0.1918,0.0834,0.0042</t>
-  </si>
-  <si>
-    <t>0.7748,0.2065,0.0333,0.0031</t>
-  </si>
-  <si>
-    <t>0.7073,0.1692,0.0870,0.0119</t>
-  </si>
-  <si>
-    <t>0.5773,0.2796,0.0840,0.0123</t>
-  </si>
-  <si>
-    <t>0.6852,0.1734,0.1840,0.0061</t>
-  </si>
-  <si>
-    <t>0.7635,0.2073,0.0403,0.0036</t>
-  </si>
-  <si>
-    <t>0.6475,0.1194,0.0506,0.0284</t>
-  </si>
-  <si>
-    <t>0.2307,0.1685,0.7828,0.0089</t>
-  </si>
-  <si>
-    <t>0.9321,0.0201,0.0091,0.0042</t>
-  </si>
-  <si>
-    <t>0.5983,0.2922,0.0812,0.0117</t>
-  </si>
-  <si>
-    <t>0.7034,0.3839,0.0390,0.0010</t>
-  </si>
-  <si>
-    <t>0.9468,0.0319,0.0133,0.0004</t>
-  </si>
-  <si>
-    <t>0.9486,0.0238,0.0158,0.0005</t>
-  </si>
-  <si>
-    <t>0.9177,0.0295,0.0322,0.0017</t>
-  </si>
-  <si>
-    <t>0.8474,0.1888,0.0219,0.0007</t>
-  </si>
-  <si>
-    <t>0.9598,0.0186,0.0106,0.0004</t>
-  </si>
-  <si>
-    <t>0.6845,0.1979,0.0492,0.0127</t>
-  </si>
-  <si>
-    <t>0.7989,0.0841,0.0446,0.0080</t>
-  </si>
-  <si>
-    <t>0.8941,0.0523,0.0267,0.0039</t>
-  </si>
-  <si>
-    <t>0.8209,0.0824,0.0405,0.0050</t>
-  </si>
-  <si>
-    <t>0.7057,0.2451,0.0545,0.0071</t>
-  </si>
-  <si>
-    <t>0.7297,0.2063,0.0611,0.0093</t>
-  </si>
-  <si>
-    <t>0.6830,0.1085,0.0449,0.0278</t>
-  </si>
-  <si>
-    <t>0.8951,0.0609,0.0270,0.0025</t>
-  </si>
-  <si>
-    <t>0.6840,0.3235,0.0573,0.0043</t>
-  </si>
-  <si>
-    <t>0.7879,0.1152,0.0286,0.0045</t>
-  </si>
-  <si>
-    <t>0.6398,0.3829,0.0837,0.0026</t>
-  </si>
-  <si>
-    <t>0.8931,0.0591,0.0108,0.0019</t>
-  </si>
-  <si>
-    <t>0.6657,0.2477,0.0926,0.0117</t>
-  </si>
-  <si>
-    <t>0.6268,0.3285,0.1188,0.0026</t>
-  </si>
-  <si>
-    <t>0.8620,0.0841,0.0245,0.0026</t>
-  </si>
-  <si>
-    <t>0.7811,0.1028,0.0785,0.0108</t>
-  </si>
-  <si>
-    <t>0.0671,0.1281,0.9484,0.0018</t>
-  </si>
-  <si>
-    <t>0.6226,0.2765,0.1498,0.0109</t>
-  </si>
-  <si>
-    <t>0.8014,0.0132,0.2338,0.0015</t>
-  </si>
-  <si>
-    <t>0.9682,0.0020,0.0335,0.0001</t>
-  </si>
-  <si>
-    <t>0.9603,0.0148,0.0188,0.0001</t>
-  </si>
-  <si>
-    <t>0.0979,0.3082,0.7750,0.0015</t>
-  </si>
-  <si>
-    <t>0.9568,0.0032,0.0578,0.0001</t>
-  </si>
-  <si>
-    <t>0.9527,0.0021,0.0599,0.0001</t>
-  </si>
-  <si>
-    <t>0.8110,0.0139,0.2348,0.0002</t>
-  </si>
-  <si>
-    <t>0.8586,0.0553,0.0911,0.0003</t>
-  </si>
-  <si>
-    <t>0.9501,0.0097,0.0317,0.0003</t>
-  </si>
-  <si>
-    <t>0.7833,0.1069,0.1442,0.0007</t>
-  </si>
-  <si>
-    <t>0.9417,0.0475,0.0153,0.0002</t>
-  </si>
-  <si>
-    <t>0.9308,0.0271,0.0356,0.0004</t>
-  </si>
-  <si>
-    <t>0.8743,0.0861,0.0513,0.0003</t>
-  </si>
-  <si>
-    <t>0.9724,0.0142,0.0090,0.0001</t>
-  </si>
-  <si>
-    <t>0.9680,0.0077,0.0184,0.0001</t>
-  </si>
-  <si>
-    <t>0.5936,0.1147,0.0672,0.0424</t>
-  </si>
-  <si>
-    <t>0.6397,0.3242,0.0549,0.0037</t>
-  </si>
-  <si>
-    <t>0.8771,0.0633,0.0359,0.0026</t>
-  </si>
-  <si>
-    <t>0.6929,0.1345,0.0737,0.0218</t>
-  </si>
-  <si>
-    <t>0.5471,0.3338,0.1210,0.0153</t>
-  </si>
-  <si>
-    <t>0.9724,0.0124,0.0104,0.0001</t>
-  </si>
-  <si>
-    <t>0.9717,0.0086,0.0127,0.0002</t>
-  </si>
-  <si>
-    <t>0.7854,0.1818,0.0733,0.0014</t>
-  </si>
-  <si>
-    <t>0.9722,0.0048,0.0191,0.0001</t>
-  </si>
-  <si>
-    <t>0.9336,0.0060,0.0707,0.0002</t>
-  </si>
-  <si>
-    <t>0.9139,0.0287,0.0499,0.0002</t>
-  </si>
-  <si>
-    <t>0.9719,0.0021,0.0272,0.0001</t>
-  </si>
-  <si>
-    <t>0.9894,0.0005,0.0075,0.0000</t>
-  </si>
-  <si>
-    <t>0.9643,0.0022,0.0303,0.0001</t>
-  </si>
-  <si>
-    <t>0.9572,0.0137,0.0184,0.0001</t>
-  </si>
-  <si>
-    <t>0.7252,0.1783,0.0701,0.0078</t>
-  </si>
-  <si>
-    <t>0.7306,0.2117,0.0478,0.0072</t>
-  </si>
-  <si>
-    <t>0.7086,0.0908,0.0369,0.0323</t>
-  </si>
-  <si>
-    <t>0.7911,0.0872,0.0422,0.0085</t>
-  </si>
-  <si>
-    <t>0.6628,0.2602,0.0820,0.0123</t>
-  </si>
-  <si>
-    <t>0.8331,0.1368,0.0215,0.0026</t>
-  </si>
-  <si>
-    <t>0.5467,0.3386,0.0658,0.0128</t>
-  </si>
-  <si>
-    <t>0.6780,0.2906,0.0608,0.0060</t>
-  </si>
-  <si>
-    <t>0.8552,0.0875,0.0242,0.0028</t>
-  </si>
-  <si>
-    <t>0.9076,0.0487,0.0289,0.0013</t>
-  </si>
-  <si>
-    <t>0.7864,0.1433,0.0852,0.0023</t>
-  </si>
-  <si>
-    <t>0.8954,0.0043,0.1205,0.0003</t>
-  </si>
-  <si>
-    <t>0.3884,0.0054,0.8184,0.0005</t>
-  </si>
-  <si>
-    <t>0.9440,0.0042,0.0602,0.0002</t>
-  </si>
-  <si>
-    <t>0.7781,0.0074,0.3434,0.0003</t>
-  </si>
-  <si>
-    <t>0.9802,0.0037,0.0115,0.0000</t>
-  </si>
-  <si>
-    <t>0.5024,0.0108,0.6908,0.0006</t>
-  </si>
-  <si>
-    <t>0.8781,0.0251,0.0719,0.0002</t>
-  </si>
-  <si>
-    <t>0.8678,0.0435,0.0928,0.0004</t>
-  </si>
-  <si>
-    <t>0.9543,0.0037,0.0320,0.0007</t>
-  </si>
-  <si>
-    <t>0.9313,0.0187,0.0538,0.0004</t>
-  </si>
-  <si>
-    <t>0.8880,0.0522,0.0489,0.0006</t>
-  </si>
-  <si>
-    <t>0.7397,0.0717,0.0257,0.0270</t>
-  </si>
-  <si>
-    <t>0.7425,0.1050,0.0509,0.0127</t>
-  </si>
-  <si>
-    <t>0.8476,0.0593,0.0256,0.0070</t>
-  </si>
-  <si>
-    <t>0.7027,0.2431,0.0485,0.0048</t>
-  </si>
-  <si>
-    <t>0.6515,0.0795,0.0295,0.0357</t>
-  </si>
-  <si>
-    <t>0.6361,0.2819,0.0616,0.0102</t>
-  </si>
-  <si>
-    <t>0.7952,0.1179,0.0270,0.0050</t>
-  </si>
-  <si>
-    <t>0.7208,0.0600,0.0246,0.0325</t>
-  </si>
-  <si>
-    <t>0.6689,0.1060,0.1497,0.0003</t>
-  </si>
-  <si>
-    <t>0.8681,0.0102,0.1684,0.0003</t>
-  </si>
-  <si>
-    <t>0.7640,0.0304,0.1902,0.0007</t>
-  </si>
-  <si>
-    <t>0.9261,0.0225,0.0426,0.0004</t>
-  </si>
-  <si>
-    <t>0.8848,0.0034,0.1601,0.0002</t>
-  </si>
-  <si>
-    <t>0.9533,0.0067,0.0318,0.0003</t>
-  </si>
-  <si>
-    <t>0.9566,0.0090,0.0258,0.0002</t>
-  </si>
-  <si>
-    <t>0.9788,0.0024,0.0106,0.0003</t>
-  </si>
-  <si>
-    <t>0.8807,0.0370,0.0219,0.0054</t>
-  </si>
-  <si>
-    <t>0.9207,0.0186,0.0168,0.0052</t>
-  </si>
-  <si>
-    <t>0.8699,0.0405,0.0632,0.0039</t>
-  </si>
-  <si>
-    <t>0.8907,0.0384,0.0429,0.0022</t>
-  </si>
-  <si>
-    <t>0.9214,0.0240,0.0212,0.0032</t>
-  </si>
-  <si>
-    <t>0.8703,0.1179,0.0314,0.0008</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9453,0.0194,0.0073,0.0168</t>
+  </si>
+  <si>
+    <t>0.0102,0.0004,0.0007,0.9960</t>
+  </si>
+  <si>
+    <t>0.8202,0.0057,0.0052,0.1593</t>
+  </si>
+  <si>
+    <t>0.3668,0.0058,0.0187,0.6932</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9914,0.0020,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.9936,0.0029,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9878,0.0067,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9913,0.0039,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9956,0.0011,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0019,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.8804,0.0220,0.0815,0.0014</t>
+  </si>
+  <si>
+    <t>0.0795,0.0173,0.9513,0.0043</t>
+  </si>
+  <si>
+    <t>0.1034,0.0277,0.9051,0.0005</t>
+  </si>
+  <si>
+    <t>0.0075,0.0014,0.9951,0.0004</t>
+  </si>
+  <si>
+    <t>0.9010,0.0085,0.0745,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.9979,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.9946,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.1575,0.8777,0.0130,0.0028</t>
+  </si>
+  <si>
+    <t>0.0021,0.9951,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.9982,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.5870,0.0091,0.5250,0.0197</t>
+  </si>
+  <si>
+    <t>0.7808,0.0052,0.1261,0.0354</t>
+  </si>
+  <si>
+    <t>0.0074,0.0012,0.9931,0.0023</t>
+  </si>
+  <si>
+    <t>0.2656,0.0042,0.8657,0.0017</t>
+  </si>
+  <si>
+    <t>0.1490,0.0011,0.9358,0.0003</t>
+  </si>
+  <si>
+    <t>0.0066,0.0017,0.9930,0.0020</t>
+  </si>
+  <si>
+    <t>0.0103,0.0027,0.9802,0.0143</t>
+  </si>
+  <si>
+    <t>0.8270,0.2517,0.0136,0.0009</t>
+  </si>
+  <si>
+    <t>0.8953,0.0207,0.0845,0.0019</t>
+  </si>
+  <si>
+    <t>0.0011,0.0061,0.9974,0.0015</t>
+  </si>
+  <si>
+    <t>0.0055,0.8035,0.3311,0.0001</t>
+  </si>
+  <si>
+    <t>0.9163,0.0150,0.0236,0.0311</t>
+  </si>
+  <si>
+    <t>0.7675,0.0382,0.1630,0.0105</t>
+  </si>
+  <si>
+    <t>0.7338,0.3655,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.0289,0.9563,0.1807,0.0026</t>
+  </si>
+  <si>
+    <t>0.0114,0.8482,0.2843,0.0712</t>
+  </si>
+  <si>
+    <t>0.0053,0.0076,0.9923,0.0029</t>
+  </si>
+  <si>
+    <t>0.0494,0.0078,0.9427,0.0167</t>
+  </si>
+  <si>
+    <t>0.0722,0.0013,0.9156,0.0191</t>
+  </si>
+  <si>
+    <t>0.0037,0.0061,0.9949,0.0004</t>
+  </si>
+  <si>
+    <t>0.0261,0.9175,0.0938,0.0045</t>
+  </si>
+  <si>
+    <t>0.0139,0.0075,0.9618,0.0202</t>
+  </si>
+  <si>
+    <t>0.0217,0.9204,0.0057,0.5297</t>
+  </si>
+  <si>
+    <t>0.0016,0.9911,0.0056,0.0103</t>
+  </si>
+  <si>
+    <t>0.0001,0.9983,0.0180,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0260,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0041,0.9936,0.0067</t>
+  </si>
+  <si>
+    <t>0.0018,0.0332,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0797,0.0149,0.9426,0.0103</t>
+  </si>
+  <si>
+    <t>0.1109,0.0036,0.9255,0.0050</t>
+  </si>
+  <si>
+    <t>0.0106,0.0186,0.9789,0.0044</t>
+  </si>
+  <si>
+    <t>0.0110,0.7925,0.7102,0.0041</t>
+  </si>
+  <si>
+    <t>0.9863,0.0130,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9786,0.0081,0.0095,0.0007</t>
+  </si>
+  <si>
+    <t>0.9687,0.0138,0.0115,0.0036</t>
+  </si>
+  <si>
+    <t>0.0126,0.0387,0.9866,0.0058</t>
+  </si>
+  <si>
+    <t>0.9896,0.0069,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9860,0.0068,0.0030,0.0033</t>
+  </si>
+  <si>
+    <t>0.9745,0.0333,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.9380,0.9849,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.5173,0.9770,0.0020</t>
+  </si>
+  <si>
+    <t>0.0047,0.0550,0.9829,0.0035</t>
+  </si>
+  <si>
+    <t>0.0001,0.9641,0.9905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0076,0.9964,0.0013</t>
+  </si>
+  <si>
+    <t>0.0132,0.9861,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.9935,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.7910,0.0092,0.3145,0.0031</t>
+  </si>
+  <si>
+    <t>0.2273,0.0894,0.8486,0.0102</t>
+  </si>
+  <si>
+    <t>0.0167,0.0249,0.9778,0.0128</t>
+  </si>
+  <si>
+    <t>0.0008,0.9671,0.8958,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9696,0.9463,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9957,0.0171,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9888,0.6962,0.0005</t>
+  </si>
+  <si>
+    <t>0.1728,0.0431,0.1536,0.6982</t>
+  </si>
+  <si>
+    <t>0.0020,0.0009,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.0055,0.0010,0.0010,0.9971</t>
+  </si>
+  <si>
+    <t>0.0020,0.0018,0.0121,0.9951</t>
+  </si>
+  <si>
+    <t>0.0020,0.0014,0.0045,0.9971</t>
+  </si>
+  <si>
+    <t>0.0048,0.0261,0.0013,0.9939</t>
+  </si>
+  <si>
+    <t>0.0002,0.9921,0.8950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.7178,0.9770,0.0008</t>
+  </si>
+  <si>
+    <t>0.0063,0.5480,0.9059,0.0007</t>
+  </si>
+  <si>
+    <t>0.0045,0.8910,0.8259,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.9902,0.5333,0.0001</t>
+  </si>
+  <si>
+    <t>0.0180,0.5031,0.7761,0.0024</t>
+  </si>
+  <si>
+    <t>0.9966,0.0017,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9766,0.0241,0.0035,0.0019</t>
+  </si>
+  <si>
+    <t>0.9828,0.0118,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9894,0.0077,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0036,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9859,0.0092,0.0024,0.0022</t>
+  </si>
+  <si>
+    <t>0.9838,0.0132,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9726,0.0267,0.0064,0.0017</t>
+  </si>
+  <si>
+    <t>0.9968,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9965,0.0010,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0006,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0005,0.9974,0.0028</t>
+  </si>
+  <si>
+    <t>0.0353,0.0084,0.9752,0.0047</t>
+  </si>
+  <si>
+    <t>0.9908,0.0013,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.0735,0.0007,0.9718,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.9909,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.0124,0.9821,0.0103,0.0011</t>
+  </si>
+  <si>
+    <t>0.0080,0.9860,0.0021,0.0035</t>
+  </si>
+  <si>
+    <t>0.0007,0.9977,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.9979,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.9947,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.6643,0.5257,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.8644,0.0196,0.1051,0.0097</t>
+  </si>
+  <si>
+    <t>0.1891,0.0115,0.8810,0.0078</t>
+  </si>
+  <si>
+    <t>0.4199,0.0384,0.0929,0.3393</t>
+  </si>
+  <si>
+    <t>0.2411,0.0418,0.7979,0.0145</t>
+  </si>
+  <si>
+    <t>0.0575,0.1384,0.0808,0.8608</t>
+  </si>
+  <si>
+    <t>0.0015,0.9950,0.0288,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.9968,0.0182,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.9961,0.0013,0.0139</t>
+  </si>
+  <si>
+    <t>0.0020,0.9612,0.7460,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.9978,0.0133,0.0001</t>
+  </si>
+  <si>
+    <t>0.9291,0.0810,0.0137,0.0048</t>
+  </si>
+  <si>
+    <t>0.8360,0.1129,0.0625,0.0093</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0016,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9914,0.0026,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.9865,0.0035,0.0057,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0026,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0021,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9898,0.0019,0.0008,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.9511,0.8460,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.8691,0.9143,0.0005</t>
+  </si>
+  <si>
+    <t>0.0055,0.0356,0.9888,0.0005</t>
+  </si>
+  <si>
+    <t>0.0984,0.0142,0.9494,0.0019</t>
+  </si>
+  <si>
+    <t>0.9679,0.0130,0.0105,0.0018</t>
+  </si>
+  <si>
+    <t>0.7173,0.0366,0.3075,0.0178</t>
+  </si>
+  <si>
+    <t>0.1879,0.0054,0.8436,0.0284</t>
+  </si>
+  <si>
+    <t>0.8196,0.0377,0.1405,0.0053</t>
+  </si>
+  <si>
+    <t>0.0163,0.0008,0.0164,0.9804</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0021,0.0042,0.0043,0.9972</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.0031,0.9979</t>
+  </si>
+  <si>
+    <t>0.0013,0.8865,0.7495,0.0058</t>
+  </si>
+  <si>
+    <t>0.9803,0.0068,0.0076,0.0032</t>
+  </si>
+  <si>
+    <t>0.2378,0.7745,0.0408,0.0298</t>
+  </si>
+  <si>
+    <t>0.9613,0.0177,0.0101,0.0109</t>
+  </si>
+  <si>
+    <t>0.6190,0.4870,0.0163,0.0084</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8234,0.0051,0.0125,0.1958</t>
+  </si>
+  <si>
+    <t>0.9581,0.0034,0.0108,0.0093</t>
+  </si>
+  <si>
+    <t>0.0025,0.1684,0.9806,0.0123</t>
+  </si>
+  <si>
+    <t>0.9186,0.0014,0.0022,0.0913</t>
+  </si>
+  <si>
+    <t>0.9361,0.0034,0.0035,0.0585</t>
+  </si>
+  <si>
+    <t>0.2394,0.7781,0.0426,0.0073</t>
+  </si>
+  <si>
+    <t>0.9257,0.0214,0.0224,0.0127</t>
+  </si>
+  <si>
+    <t>0.9771,0.0064,0.0107,0.0008</t>
+  </si>
+  <si>
+    <t>0.1362,0.7449,0.1428,0.0219</t>
+  </si>
+  <si>
+    <t>0.9306,0.0385,0.0257,0.0014</t>
+  </si>
+  <si>
+    <t>0.9832,0.0080,0.0038,0.0012</t>
+  </si>
+  <si>
+    <t>0.9926,0.0003,0.0014,0.0019</t>
+  </si>
+  <si>
+    <t>0.9966,0.0012,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9892,0.0018,0.0015,0.0033</t>
+  </si>
+  <si>
+    <t>0.9929,0.0011,0.0008,0.0028</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9824,0.0080,0.0057,0.0023</t>
+  </si>
+  <si>
+    <t>0.9934,0.0006,0.0004,0.0033</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9458,0.0445,0.0034,0.0032</t>
+  </si>
+  <si>
+    <t>0.7927,0.3657,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9132,0.1164,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.2469,0.1932,0.7374,0.0116</t>
+  </si>
+  <si>
+    <t>0.9920,0.0044,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9734,0.0285,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9810,0.0149,0.0035,0.0014</t>
+  </si>
+  <si>
+    <t>0.9894,0.0047,0.0009,0.0023</t>
+  </si>
+  <si>
+    <t>0.0008,0.0032,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9213,0.1087,0.0044,0.0021</t>
+  </si>
+  <si>
+    <t>0.0079,0.0029,0.9931,0.0019</t>
+  </si>
+  <si>
+    <t>0.0077,0.0053,0.9896,0.0027</t>
+  </si>
+  <si>
+    <t>0.1338,0.0010,0.9066,0.0066</t>
+  </si>
+  <si>
+    <t>0.0025,0.1414,0.9860,0.0027</t>
+  </si>
+  <si>
+    <t>0.0716,0.0044,0.9694,0.0011</t>
+  </si>
+  <si>
+    <t>0.0566,0.0015,0.9751,0.0004</t>
+  </si>
+  <si>
+    <t>0.0133,0.0111,0.9850,0.0048</t>
+  </si>
+  <si>
+    <t>0.0549,0.0239,0.9351,0.0065</t>
+  </si>
+  <si>
+    <t>0.3749,0.0512,0.6705,0.0099</t>
+  </si>
+  <si>
+    <t>0.1362,0.0247,0.8923,0.0229</t>
+  </si>
+  <si>
+    <t>0.1563,0.3771,0.4672,0.0028</t>
+  </si>
+  <si>
+    <t>0.1031,0.6473,0.5364,0.0173</t>
+  </si>
+  <si>
+    <t>0.5846,0.0166,0.4676,0.0011</t>
+  </si>
+  <si>
+    <t>0.5502,0.3235,0.1595,0.0234</t>
+  </si>
+  <si>
+    <t>0.0592,0.0280,0.9344,0.0090</t>
+  </si>
+  <si>
+    <t>0.0159,0.9853,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.9841,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.7628,0.3588,0.0025,0.0023</t>
+  </si>
+  <si>
+    <t>0.8268,0.2615,0.0058,0.0015</t>
+  </si>
+  <si>
+    <t>0.4349,0.6760,0.0116,0.0062</t>
+  </si>
+  <si>
+    <t>0.7994,0.0419,0.1716,0.0079</t>
+  </si>
+  <si>
+    <t>0.9937,0.0015,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.8895,0.0070,0.0131,0.0573</t>
+  </si>
+  <si>
+    <t>0.9413,0.0010,0.0882,0.0002</t>
+  </si>
+  <si>
+    <t>0.4571,0.0025,0.5129,0.0280</t>
+  </si>
+  <si>
+    <t>0.0121,0.0045,0.9864,0.0068</t>
+  </si>
+  <si>
+    <t>0.0098,0.0179,0.9593,0.0304</t>
+  </si>
+  <si>
+    <t>0.1079,0.0404,0.9032,0.0132</t>
+  </si>
+  <si>
+    <t>0.1304,0.0055,0.9220,0.0036</t>
+  </si>
+  <si>
+    <t>0.0131,0.0668,0.9560,0.0047</t>
+  </si>
+  <si>
+    <t>0.9931,0.0036,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9865,0.0093,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9780,0.0136,0.0065,0.0034</t>
+  </si>
+  <si>
+    <t>0.9144,0.0774,0.0124,0.0108</t>
+  </si>
+  <si>
+    <t>0.9798,0.0175,0.0029,0.0026</t>
+  </si>
+  <si>
+    <t>0.9887,0.0030,0.0016,0.0031</t>
+  </si>
+  <si>
+    <t>0.9872,0.0085,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.0483,0.0037,0.9727,0.0088</t>
+  </si>
+  <si>
+    <t>0.1585,0.5849,0.5301,0.0643</t>
+  </si>
+  <si>
+    <t>0.9688,0.0090,0.0137,0.0017</t>
+  </si>
+  <si>
+    <t>0.0315,0.0115,0.9765,0.0013</t>
+  </si>
+  <si>
+    <t>0.0010,0.0028,0.9937,0.0092</t>
+  </si>
+  <si>
+    <t>0.0741,0.0548,0.8984,0.0130</t>
+  </si>
+  <si>
+    <t>0.0191,0.0128,0.9843,0.0011</t>
+  </si>
+  <si>
+    <t>0.0769,0.0045,0.9532,0.0040</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9989,0.0007</t>
+  </si>
+  <si>
+    <t>0.0130,0.0118,0.9824,0.0052</t>
+  </si>
+  <si>
+    <t>0.1082,0.0447,0.8401,0.0043</t>
+  </si>
+  <si>
+    <t>0.8733,0.0084,0.1491,0.0025</t>
+  </si>
+  <si>
+    <t>0.9008,0.0015,0.1471,0.0008</t>
+  </si>
+  <si>
+    <t>0.9850,0.0027,0.0065,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0041,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0045,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9868,0.0089,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0009,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9962,0.0018,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9936,0.0050,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9864,0.0156,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0152,0.2399,0.9192,0.0063</t>
+  </si>
+  <si>
+    <t>0.0030,0.4824,0.9664,0.0018</t>
+  </si>
+  <si>
+    <t>0.0048,0.0160,0.9880,0.0019</t>
+  </si>
+  <si>
+    <t>0.0944,0.0231,0.9086,0.0023</t>
+  </si>
+  <si>
+    <t>0.0073,0.0113,0.9910,0.0017</t>
+  </si>
+  <si>
+    <t>0.0379,0.0015,0.8777,0.1080</t>
+  </si>
+  <si>
+    <t>0.1136,0.0023,0.9589,0.0018</t>
+  </si>
+  <si>
+    <t>0.2074,0.0102,0.7244,0.0540</t>
+  </si>
+  <si>
+    <t>0.8677,0.0013,0.0156,0.0574</t>
+  </si>
+  <si>
+    <t>0.1198,0.0081,0.0013,0.9289</t>
+  </si>
+  <si>
+    <t>0.0071,0.0009,0.0187,0.9870</t>
+  </si>
+  <si>
+    <t>0.0131,0.0015,0.0039,0.9906</t>
+  </si>
+  <si>
+    <t>0.0047,0.0001,0.0014,0.9968</t>
+  </si>
+  <si>
+    <t>0.9716,0.0038,0.0039,0.0075</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,10 +5106,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
